--- a/SWESMS-System/ganttchart/Project Gantt Chart and Daily Breakdown.xlsx
+++ b/SWESMS-System/ganttchart/Project Gantt Chart and Daily Breakdown.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\assigments\SWESMS-System\ganttchart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10D9A38-3487-4405-AC30-88818CEE4759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4117A99-CAE5-4945-9125-837D66A13E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
   <si>
     <t>Main Task</t>
   </si>
@@ -200,6 +200,30 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF356854"/>
@@ -215,37 +239,13 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Project Gantt Chart and Daily B-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="10"/>
-      <tableStyleElement type="firstRowStripe" dxfId="9"/>
-      <tableStyleElement type="secondRowStripe" dxfId="8"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="10"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="secondRowStripe" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -756,8 +756,12 @@
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="I15" s="3" t="s">
         <v>11</v>
       </c>
